--- a/artfynd/A 43645-2026 artfynd.xlsx
+++ b/artfynd/A 43645-2026 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>136984187</v>
       </c>
       <c r="B3" t="n">
-        <v>102866</v>
+        <v>102872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43645-2026 artfynd.xlsx
+++ b/artfynd/A 43645-2026 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>136984187</v>
       </c>
       <c r="B3" t="n">
-        <v>102872</v>
+        <v>102884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43645-2026 artfynd.xlsx
+++ b/artfynd/A 43645-2026 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>136984187</v>
       </c>
       <c r="B3" t="n">
-        <v>102884</v>
+        <v>102885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43645-2026 artfynd.xlsx
+++ b/artfynd/A 43645-2026 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>136984187</v>
       </c>
       <c r="B3" t="n">
-        <v>102885</v>
+        <v>102888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43645-2026 artfynd.xlsx
+++ b/artfynd/A 43645-2026 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>136984187</v>
       </c>
       <c r="B3" t="n">
-        <v>102888</v>
+        <v>102889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43645-2026 artfynd.xlsx
+++ b/artfynd/A 43645-2026 artfynd.xlsx
@@ -828,7 +828,7 @@
         <v>136984187</v>
       </c>
       <c r="B3" t="n">
-        <v>102889</v>
+        <v>102892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
